--- a/40_Threshold_OUTPUT/direct_Q7CFV3_Yersinia_pestis_biovar_Microtus_str__91001.xlsx
+++ b/40_Threshold_OUTPUT/direct_Q7CFV3_Yersinia_pestis_biovar_Microtus_str__91001.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I22"/>
+  <dimension ref="A1:J22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -469,6 +469,11 @@
           <t>p_value</t>
         </is>
       </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>evaluation</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
@@ -508,6 +513,11 @@
       <c r="I2" t="n">
         <v>0.9960015993602559</v>
       </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Confirmed DR</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
@@ -547,6 +557,11 @@
       <c r="I3" t="n">
         <v>0.9960015993602559</v>
       </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Confirmed DR</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
@@ -585,6 +600,11 @@
       </c>
       <c r="I4" t="n">
         <v>0.9960015993602559</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Confirmed DR</t>
+        </is>
       </c>
     </row>
     <row r="5">
@@ -625,6 +645,11 @@
       <c r="I5" t="n">
         <v>0.9998000799680128</v>
       </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Confirmed DR</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
@@ -664,6 +689,11 @@
       <c r="I6" t="n">
         <v>0.9998000799680128</v>
       </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Confirmed DR</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
@@ -703,6 +733,11 @@
       <c r="I7" t="n">
         <v>0.9998000799680128</v>
       </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Confirmed DR</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
@@ -742,6 +777,11 @@
       <c r="I8" t="n">
         <v>0.9998000799680128</v>
       </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Confirmed DR</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
@@ -781,6 +821,11 @@
       <c r="I9" t="n">
         <v>0.9998000799680128</v>
       </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Confirmed DR</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
@@ -820,6 +865,11 @@
       <c r="I10" t="n">
         <v>0.9998000799680128</v>
       </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Confirmed DR</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
@@ -859,6 +909,11 @@
       <c r="I11" t="n">
         <v>0.9998000799680128</v>
       </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Confirmed DR</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
@@ -898,6 +953,11 @@
       <c r="I12" t="n">
         <v>0.9998000799680128</v>
       </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Confirmed DR</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
@@ -937,6 +997,11 @@
       <c r="I13" t="n">
         <v>0.9998000799680128</v>
       </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Confirmed DR</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
@@ -976,6 +1041,11 @@
       <c r="I14" t="n">
         <v>0.9998000799680128</v>
       </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Confirmed DR</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
@@ -1015,6 +1085,11 @@
       <c r="I15" t="n">
         <v>0.9998000799680128</v>
       </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Confirmed DR</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
@@ -1054,6 +1129,11 @@
       <c r="I16" t="n">
         <v>0.9998000799680128</v>
       </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Confirmed DR</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
@@ -1093,6 +1173,11 @@
       <c r="I17" t="n">
         <v>0.9998000799680128</v>
       </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Confirmed DR</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
@@ -1132,6 +1217,11 @@
       <c r="I18" t="n">
         <v>0.9998000799680128</v>
       </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Confirmed DR</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
@@ -1171,6 +1261,11 @@
       <c r="I19" t="n">
         <v>0.9998000799680128</v>
       </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Confirmed DR</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
@@ -1210,6 +1305,11 @@
       <c r="I20" t="n">
         <v>0.9998000799680128</v>
       </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Confirmed DR</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
@@ -1249,6 +1349,11 @@
       <c r="I21" t="n">
         <v>0.9998000799680128</v>
       </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Confirmed DR</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
@@ -1287,6 +1392,11 @@
       </c>
       <c r="I22" t="n">
         <v>0.9998000799680128</v>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Confirmed DR</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/40_Threshold_OUTPUT/direct_Q7CFV3_Yersinia_pestis_biovar_Microtus_str__91001.xlsx
+++ b/40_Threshold_OUTPUT/direct_Q7CFV3_Yersinia_pestis_biovar_Microtus_str__91001.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J22"/>
+  <dimension ref="A1:K22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -474,6 +474,11 @@
           <t>evaluation</t>
         </is>
       </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>correctness_%</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
@@ -518,6 +523,9 @@
           <t>Confirmed DR</t>
         </is>
       </c>
+      <c r="K2" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
@@ -562,6 +570,9 @@
           <t>Confirmed DR</t>
         </is>
       </c>
+      <c r="K3" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
@@ -605,6 +616,9 @@
         <is>
           <t>Confirmed DR</t>
         </is>
+      </c>
+      <c r="K4" t="n">
+        <v>100</v>
       </c>
     </row>
     <row r="5">
@@ -650,6 +664,9 @@
           <t>Confirmed DR</t>
         </is>
       </c>
+      <c r="K5" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
@@ -694,6 +711,9 @@
           <t>Confirmed DR</t>
         </is>
       </c>
+      <c r="K6" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
@@ -738,6 +758,9 @@
           <t>Confirmed DR</t>
         </is>
       </c>
+      <c r="K7" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
@@ -782,6 +805,9 @@
           <t>Confirmed DR</t>
         </is>
       </c>
+      <c r="K8" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
@@ -826,6 +852,9 @@
           <t>Confirmed DR</t>
         </is>
       </c>
+      <c r="K9" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
@@ -870,6 +899,9 @@
           <t>Confirmed DR</t>
         </is>
       </c>
+      <c r="K10" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
@@ -914,6 +946,9 @@
           <t>Confirmed DR</t>
         </is>
       </c>
+      <c r="K11" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
@@ -958,6 +993,9 @@
           <t>Confirmed DR</t>
         </is>
       </c>
+      <c r="K12" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
@@ -1002,6 +1040,9 @@
           <t>Confirmed DR</t>
         </is>
       </c>
+      <c r="K13" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
@@ -1046,6 +1087,9 @@
           <t>Confirmed DR</t>
         </is>
       </c>
+      <c r="K14" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
@@ -1090,6 +1134,9 @@
           <t>Confirmed DR</t>
         </is>
       </c>
+      <c r="K15" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
@@ -1134,6 +1181,9 @@
           <t>Confirmed DR</t>
         </is>
       </c>
+      <c r="K16" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
@@ -1178,6 +1228,9 @@
           <t>Confirmed DR</t>
         </is>
       </c>
+      <c r="K17" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
@@ -1222,6 +1275,9 @@
           <t>Confirmed DR</t>
         </is>
       </c>
+      <c r="K18" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
@@ -1266,6 +1322,9 @@
           <t>Confirmed DR</t>
         </is>
       </c>
+      <c r="K19" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
@@ -1310,6 +1369,9 @@
           <t>Confirmed DR</t>
         </is>
       </c>
+      <c r="K20" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
@@ -1354,6 +1416,9 @@
           <t>Confirmed DR</t>
         </is>
       </c>
+      <c r="K21" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
@@ -1397,6 +1462,9 @@
         <is>
           <t>Confirmed DR</t>
         </is>
+      </c>
+      <c r="K22" t="n">
+        <v>100</v>
       </c>
     </row>
   </sheetData>
